--- a/shared/words/E7_单词汇总.xlsx
+++ b/shared/words/E7_单词汇总.xlsx
@@ -1148,6 +1148,11 @@
           <t>words/einheit7/grüßen.mp3</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ich grüße dich herzlich.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="14.15" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -1172,6 +1177,11 @@
           <t>words/einheit7/schenken.mp3</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Was willst du ihr denn schenken?</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="14.15" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -1196,6 +1206,11 @@
           <t>words/einheit7/wissen.mp3</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weißt du, wo er wohnt?</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="14.15" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -1220,6 +1235,11 @@
           <t>words/einheit7/tragen.mp3</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Er trägt eine Brille.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="14.15" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -2095,6 +2115,11 @@
           <t>words/einheit7/Wochenende.mp3</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Schönes Wochenende!</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="14.15" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
@@ -2156,6 +2181,11 @@
           <t>words/einheit7/alle.mp3</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alle Studenten sind da.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="14.15" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
@@ -2180,6 +2210,11 @@
           <t>words/einheit7/rot.mp3</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Rose ist rot.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="14.15" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -2320,6 +2355,11 @@
           <t>words/einheit7/unterwegs.mp3</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Man muss es unterwegs immer mitnehmen.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="14.15" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
@@ -2344,6 +2384,11 @@
           <t>words/einheit7/typisch.mp3</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das ist typisch für ihn.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="14.15" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -2368,6 +2413,11 @@
           <t>words/einheit7/grün.mp3</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Das Haus liegt auf der grünen Wiese.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="14.15" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
@@ -2392,6 +2442,11 @@
           <t>words/einheit7/gelb.mp3</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Banane ist gelb.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="14.15" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -2414,6 +2469,11 @@
       <c r="F41" t="inlineStr">
         <is>
           <t>words/einheit7/bunt.mp3</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Die Blumen sind bunt.</t>
         </is>
       </c>
     </row>
